--- a/Proiect/Proiect/Output/Rapoarte/Rezultate_Regresie_Simplu.xlsx
+++ b/Proiect/Proiect/Output/Rapoarte/Rezultate_Regresie_Simplu.xlsx
@@ -7,8 +7,7 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Coeficienti" sheetId="1" r:id="rId1"/>
-    <sheet name="Sumar" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -389,16 +388,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>5.165743473868366</v>
+        <v>5.806244072159987</v>
       </c>
       <c r="C2">
-        <v>0.7830576688597849</v>
+        <v>1.346724382860848</v>
       </c>
       <c r="D2">
-        <v>6.596887661403326</v>
+        <v>4.311382600666796</v>
       </c>
       <c r="E2">
-        <v>3.141968747286413E-07</v>
+        <v>0.0001526826557540163</v>
       </c>
     </row>
     <row r="3">
@@ -408,126 +407,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.089596604267779</v>
+        <v>0.8709587235665222</v>
       </c>
       <c r="C3">
-        <v>0.1470427986524887</v>
+        <v>0.2399543725740631</v>
       </c>
       <c r="D3">
-        <v>7.410064377534463</v>
+        <v>3.629684736408362</v>
       </c>
       <c r="E3">
-        <v>3.643316913770036E-08</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>r.squared</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>adj.r.squared</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>statistic</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>p.value</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>df</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>logLik</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>AIC</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>BIC</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>deviance</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>df.residual</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>nobs</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>0.6543877139572363</v>
-      </c>
-      <c r="B2">
-        <v>0.6424700489212789</v>
-      </c>
-      <c r="C2">
-        <v>1.168953089386606</v>
-      </c>
-      <c r="D2">
-        <v>54.90905407920518</v>
-      </c>
-      <c r="E2">
-        <v>3.643316913770049E-08</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>-47.79274336281764</v>
-      </c>
-      <c r="H2">
-        <v>101.5854867256353</v>
-      </c>
-      <c r="I2">
-        <v>105.8874483390907</v>
-      </c>
-      <c r="J2">
-        <v>39.62708843040826</v>
-      </c>
-      <c r="K2">
-        <v>29</v>
-      </c>
-      <c r="L2">
-        <v>31</v>
+        <v>0.001010276301508495</v>
       </c>
     </row>
   </sheetData>
